--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/pre LAM_HRM-2031-0140/panel_11/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/pre LAM_HRM-2031-0140/panel_11/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Back_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,11 +437,21 @@
           <t>Radius</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Unit 7</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -450,72 +460,72 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.64209</v>
+        <v>16.79726</v>
       </c>
       <c r="D2" t="n">
-        <v>16.84119</v>
+        <v>16.43933</v>
       </c>
       <c r="E2" t="n">
-        <v>16.44398</v>
+        <v>16.47207</v>
       </c>
       <c r="F2" t="n">
-        <v>41.99754</v>
+        <v>42.24402</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05056</v>
+        <v>0.05057</v>
       </c>
       <c r="H2" t="n">
-        <v>1.80186</v>
+        <v>1.84531</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.98563</v>
+        <v>16.84418</v>
       </c>
       <c r="D3" t="n">
-        <v>16.55844</v>
+        <v>16.55529</v>
       </c>
       <c r="E3" t="n">
-        <v>16.82877</v>
+        <v>16.84095</v>
       </c>
       <c r="F3" t="n">
-        <v>42.08135</v>
+        <v>43.35311</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05154</v>
+        <v>0.05051</v>
       </c>
       <c r="H3" t="n">
-        <v>1.81814</v>
+        <v>1.8237</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.89255</v>
+        <v>16.93052</v>
       </c>
       <c r="D4" t="n">
-        <v>16.48099</v>
+        <v>16.14415</v>
       </c>
       <c r="E4" t="n">
-        <v>16.62702</v>
+        <v>16.83783</v>
       </c>
       <c r="F4" t="n">
-        <v>42.1643</v>
+        <v>42.36016</v>
       </c>
       <c r="G4" t="n">
         <v>0.05032</v>
       </c>
       <c r="H4" t="n">
-        <v>1.85355</v>
+        <v>1.82401</v>
       </c>
     </row>
     <row r="5">
@@ -525,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.57863</v>
+        <v>17.09465</v>
       </c>
       <c r="D5" t="n">
-        <v>16.57488</v>
+        <v>16.77175</v>
       </c>
       <c r="E5" t="n">
-        <v>16.41915</v>
+        <v>16.86089</v>
       </c>
       <c r="F5" t="n">
-        <v>42.68794</v>
+        <v>41.80449</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05083</v>
+        <v>0.05009</v>
       </c>
       <c r="H5" t="n">
-        <v>1.81349</v>
+        <v>1.83741</v>
       </c>
     </row>
     <row r="6">
@@ -550,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.09464</v>
+        <v>16.9467</v>
       </c>
       <c r="D6" t="n">
-        <v>16.65852</v>
+        <v>16.65076</v>
       </c>
       <c r="E6" t="n">
-        <v>17.10507</v>
+        <v>16.88425</v>
       </c>
       <c r="F6" t="n">
-        <v>42.16907</v>
+        <v>43.18824</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04958</v>
+        <v>0.05104</v>
       </c>
       <c r="H6" t="n">
-        <v>1.78913</v>
+        <v>1.82615</v>
       </c>
     </row>
     <row r="7">
@@ -575,231 +585,1596 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.49716</v>
+        <v>16.69015</v>
       </c>
       <c r="D7" t="n">
-        <v>16.44115</v>
+        <v>16.40089</v>
       </c>
       <c r="E7" t="n">
-        <v>16.79991</v>
+        <v>16.44391</v>
       </c>
       <c r="F7" t="n">
-        <v>43.34424</v>
+        <v>42.56003</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05014</v>
+        <v>0.05087</v>
       </c>
       <c r="H7" t="n">
-        <v>1.80574</v>
+        <v>1.78998</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 7</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.89849</v>
+        <v>16.80986</v>
       </c>
       <c r="D8" t="n">
-        <v>16.63686</v>
+        <v>16.5531</v>
       </c>
       <c r="E8" t="n">
-        <v>16.46646</v>
+        <v>16.75638</v>
       </c>
       <c r="F8" t="n">
-        <v>41.92716</v>
+        <v>42.34407</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05103</v>
+        <v>0.05181</v>
       </c>
       <c r="H8" t="n">
-        <v>1.83383</v>
+        <v>1.82522</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.8055</v>
+        <v>17.08834</v>
       </c>
       <c r="D9" t="n">
-        <v>16.82372</v>
+        <v>16.37137</v>
       </c>
       <c r="E9" t="n">
-        <v>16.84634</v>
+        <v>16.73298</v>
       </c>
       <c r="F9" t="n">
-        <v>42.24684</v>
+        <v>42.688</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05076</v>
+        <v>0.04971</v>
       </c>
       <c r="H9" t="n">
-        <v>1.83932</v>
+        <v>1.80959</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Unit 3</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.58902</v>
+        <v>16.78201</v>
       </c>
       <c r="D10" t="n">
-        <v>16.55057</v>
+        <v>16.36413</v>
       </c>
       <c r="E10" t="n">
-        <v>16.61598</v>
+        <v>16.69787</v>
       </c>
       <c r="F10" t="n">
-        <v>43.20541</v>
+        <v>42.53604</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05009</v>
+        <v>0.0496</v>
       </c>
       <c r="H10" t="n">
-        <v>1.83845</v>
+        <v>1.81662</v>
       </c>
     </row>
     <row r="11">
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Unit 10</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>17.17999</v>
+      </c>
+      <c r="D11" t="n">
+        <v>16.31247</v>
+      </c>
+      <c r="E11" t="n">
+        <v>16.57366</v>
+      </c>
+      <c r="F11" t="n">
+        <v>41.55125</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.05085</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.82281</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>via 1</t>
+          <t>Unit 11</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.60095</v>
+        <v>16.74352</v>
       </c>
       <c r="D12" t="n">
-        <v>1.12405</v>
+        <v>16.53196</v>
+      </c>
+      <c r="E12" t="n">
+        <v>16.72609</v>
+      </c>
+      <c r="F12" t="n">
+        <v>43.62256</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.04935</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.82783</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 12</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.60503</v>
+        <v>16.80462</v>
       </c>
       <c r="D13" t="n">
-        <v>1.09334</v>
+        <v>16.30153</v>
+      </c>
+      <c r="E13" t="n">
+        <v>16.73974</v>
+      </c>
+      <c r="F13" t="n">
+        <v>41.84866</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.05065</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.83105</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 13</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.59623</v>
+        <v>16.74235</v>
       </c>
       <c r="D14" t="n">
-        <v>1.09971</v>
+        <v>16.48008</v>
+      </c>
+      <c r="E14" t="n">
+        <v>16.69023</v>
+      </c>
+      <c r="F14" t="n">
+        <v>42.50344</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.05097</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.80702</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 14</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.60653</v>
+        <v>16.92283</v>
       </c>
       <c r="D15" t="n">
-        <v>1.10053</v>
+        <v>16.54651</v>
+      </c>
+      <c r="E15" t="n">
+        <v>16.92217</v>
+      </c>
+      <c r="F15" t="n">
+        <v>43.71153</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.04916</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.81401</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 15</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.606</v>
+        <v>17.04194</v>
       </c>
       <c r="D16" t="n">
-        <v>1.11019</v>
+        <v>16.42782</v>
+      </c>
+      <c r="E16" t="n">
+        <v>16.44791</v>
+      </c>
+      <c r="F16" t="n">
+        <v>42.49863</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.05034</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.80997</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 16</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.602</v>
+        <v>17.07044</v>
       </c>
       <c r="D17" t="n">
-        <v>1.10893</v>
+        <v>16.44797</v>
+      </c>
+      <c r="E17" t="n">
+        <v>16.52671</v>
+      </c>
+      <c r="F17" t="n">
+        <v>41.57279</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.05017</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.83302</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 17</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.61531</v>
+        <v>16.83469</v>
       </c>
       <c r="D18" t="n">
-        <v>1.10912</v>
+        <v>16.50978</v>
+      </c>
+      <c r="E18" t="n">
+        <v>16.79057</v>
+      </c>
+      <c r="F18" t="n">
+        <v>43.39262</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.05133</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.84946</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 18</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.59505</v>
+        <v>16.91759</v>
       </c>
       <c r="D19" t="n">
-        <v>1.09229</v>
+        <v>16.41992</v>
+      </c>
+      <c r="E19" t="n">
+        <v>16.57036</v>
+      </c>
+      <c r="F19" t="n">
+        <v>42.25727</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.05096</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.82306</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Unit 19</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>16.46428</v>
+      </c>
+      <c r="D20" t="n">
+        <v>16.38718</v>
+      </c>
+      <c r="E20" t="n">
+        <v>16.3944</v>
+      </c>
+      <c r="F20" t="n">
+        <v>42.15913</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.05079</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.7956</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Unit 20</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>16.67411</v>
+      </c>
+      <c r="D21" t="n">
+        <v>16.32793</v>
+      </c>
+      <c r="E21" t="n">
+        <v>16.42414</v>
+      </c>
+      <c r="F21" t="n">
+        <v>42.97921</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.04997</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.81103</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Unit 21</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>17.32929</v>
+      </c>
+      <c r="D22" t="n">
+        <v>16.53474</v>
+      </c>
+      <c r="E22" t="n">
+        <v>16.69949</v>
+      </c>
+      <c r="F22" t="n">
+        <v>42.0174</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.05023</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.75785</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Unit 22</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>16.80324</v>
+      </c>
+      <c r="D23" t="n">
+        <v>16.73166</v>
+      </c>
+      <c r="E23" t="n">
+        <v>16.78901</v>
+      </c>
+      <c r="F23" t="n">
+        <v>42.59419</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.05016</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.80282</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Unit 23</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>16.77371</v>
+      </c>
+      <c r="D24" t="n">
+        <v>16.58452</v>
+      </c>
+      <c r="E24" t="n">
+        <v>16.70282</v>
+      </c>
+      <c r="F24" t="n">
+        <v>41.60555</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.05018</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.8101</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Unit 24</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>17.17609</v>
+      </c>
+      <c r="D25" t="n">
+        <v>16.42727</v>
+      </c>
+      <c r="E25" t="n">
+        <v>16.92558</v>
+      </c>
+      <c r="F25" t="n">
+        <v>42.849</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.05031</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.84787</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Unit 25</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>17.00237</v>
+      </c>
+      <c r="D26" t="n">
+        <v>16.63194</v>
+      </c>
+      <c r="E26" t="n">
+        <v>16.97081</v>
+      </c>
+      <c r="F26" t="n">
+        <v>42.7124</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.05078</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.7965</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Unit 26</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>16.93171</v>
+      </c>
+      <c r="D27" t="n">
+        <v>16.64414</v>
+      </c>
+      <c r="E27" t="n">
+        <v>16.80155</v>
+      </c>
+      <c r="F27" t="n">
+        <v>42.26704</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.05046</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.78986</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Unit 27</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>16.84604</v>
+      </c>
+      <c r="D28" t="n">
+        <v>16.77337</v>
+      </c>
+      <c r="E28" t="n">
+        <v>16.80399</v>
+      </c>
+      <c r="F28" t="n">
+        <v>42.53528</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.05048</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.82313</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Unit 28</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>16.97693</v>
+      </c>
+      <c r="D29" t="n">
+        <v>16.22311</v>
+      </c>
+      <c r="E29" t="n">
+        <v>16.91347</v>
+      </c>
+      <c r="F29" t="n">
+        <v>42.66764</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.05069</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.79888</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Unit 29</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>16.95508</v>
+      </c>
+      <c r="D30" t="n">
+        <v>16.67389</v>
+      </c>
+      <c r="E30" t="n">
+        <v>16.75272</v>
+      </c>
+      <c r="F30" t="n">
+        <v>43.28152</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.05003</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.8064</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Unit 30</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>17.05009</v>
+      </c>
+      <c r="D31" t="n">
+        <v>16.88461</v>
+      </c>
+      <c r="E31" t="n">
+        <v>16.96581</v>
+      </c>
+      <c r="F31" t="n">
+        <v>42.60138</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.05063</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.82061</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unit 31</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>16.95352</v>
+      </c>
+      <c r="D32" t="n">
+        <v>16.68306</v>
+      </c>
+      <c r="E32" t="n">
+        <v>16.75747</v>
+      </c>
+      <c r="F32" t="n">
+        <v>42.29626</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.05046</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.82196</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unit 32</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>16.86169</v>
+      </c>
+      <c r="D33" t="n">
+        <v>16.58102</v>
+      </c>
+      <c r="E33" t="n">
+        <v>16.69724</v>
+      </c>
+      <c r="F33" t="n">
+        <v>42.89675</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.05069</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.78929</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unit 33</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>16.99761</v>
+      </c>
+      <c r="D34" t="n">
+        <v>16.38181</v>
+      </c>
+      <c r="E34" t="n">
+        <v>16.98546</v>
+      </c>
+      <c r="F34" t="n">
+        <v>42.79509</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.05081</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.84442</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unit 34</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>17.21712</v>
+      </c>
+      <c r="D35" t="n">
+        <v>16.69536</v>
+      </c>
+      <c r="E35" t="n">
+        <v>16.90466</v>
+      </c>
+      <c r="F35" t="n">
+        <v>41.68416</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.05159</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.83004</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unit 35</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>16.88687</v>
+      </c>
+      <c r="D36" t="n">
+        <v>16.70165</v>
+      </c>
+      <c r="E36" t="n">
+        <v>16.81161</v>
+      </c>
+      <c r="F36" t="n">
+        <v>41.89993</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.05099</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.80779</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unit 36</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>16.76864</v>
+      </c>
+      <c r="D37" t="n">
+        <v>16.60573</v>
+      </c>
+      <c r="E37" t="n">
+        <v>16.73896</v>
+      </c>
+      <c r="F37" t="n">
+        <v>42.11012</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.04997</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.85673</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Trace 1</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>16.41184</v>
+      </c>
+      <c r="D39" t="n">
+        <v>15.62012</v>
+      </c>
+      <c r="E39" t="n">
+        <v>16.39797</v>
+      </c>
+      <c r="F39" t="n">
+        <v>21.54925</v>
+      </c>
+      <c r="G39" t="n">
+        <v>34.11816</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>16.92856</v>
+      </c>
+      <c r="D40" t="n">
+        <v>16.15243</v>
+      </c>
+      <c r="E40" t="n">
+        <v>16.37055</v>
+      </c>
+      <c r="F40" t="n">
+        <v>21.67765</v>
+      </c>
+      <c r="G40" t="n">
+        <v>34.06405</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C20" t="n">
-        <v>0.60407</v>
-      </c>
-      <c r="D20" t="n">
-        <v>1.10508</v>
+      <c r="C41" t="n">
+        <v>16.87642</v>
+      </c>
+      <c r="D41" t="n">
+        <v>16.00857</v>
+      </c>
+      <c r="E41" t="n">
+        <v>16.35583</v>
+      </c>
+      <c r="F41" t="n">
+        <v>21.67816</v>
+      </c>
+      <c r="G41" t="n">
+        <v>34.44396</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>16.70806</v>
+      </c>
+      <c r="D42" t="n">
+        <v>15.71605</v>
+      </c>
+      <c r="E42" t="n">
+        <v>16.41216</v>
+      </c>
+      <c r="F42" t="n">
+        <v>21.95217</v>
+      </c>
+      <c r="G42" t="n">
+        <v>33.88537</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>16.72357</v>
+      </c>
+      <c r="D43" t="n">
+        <v>15.88276</v>
+      </c>
+      <c r="E43" t="n">
+        <v>16.50723</v>
+      </c>
+      <c r="F43" t="n">
+        <v>21.44191</v>
+      </c>
+      <c r="G43" t="n">
+        <v>34.03241</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>16.89242</v>
+      </c>
+      <c r="D44" t="n">
+        <v>16.24184</v>
+      </c>
+      <c r="E44" t="n">
+        <v>16.25108</v>
+      </c>
+      <c r="F44" t="n">
+        <v>22.00753</v>
+      </c>
+      <c r="G44" t="n">
+        <v>34.7121</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>16.89308</v>
+      </c>
+      <c r="D45" t="n">
+        <v>16.18545</v>
+      </c>
+      <c r="E45" t="n">
+        <v>16.18856</v>
+      </c>
+      <c r="F45" t="n">
+        <v>21.9649</v>
+      </c>
+      <c r="G45" t="n">
+        <v>33.92909</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>16.79759</v>
+      </c>
+      <c r="D46" t="n">
+        <v>15.65791</v>
+      </c>
+      <c r="E46" t="n">
+        <v>16.31549</v>
+      </c>
+      <c r="F46" t="n">
+        <v>21.49634</v>
+      </c>
+      <c r="G46" t="n">
+        <v>34.21201</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>16.32602</v>
+      </c>
+      <c r="D47" t="n">
+        <v>15.81797</v>
+      </c>
+      <c r="E47" t="n">
+        <v>16.24177</v>
+      </c>
+      <c r="F47" t="n">
+        <v>21.60854</v>
+      </c>
+      <c r="G47" t="n">
+        <v>33.9768</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unit 10</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>16.61577</v>
+      </c>
+      <c r="D48" t="n">
+        <v>16.33413</v>
+      </c>
+      <c r="E48" t="n">
+        <v>16.43794</v>
+      </c>
+      <c r="F48" t="n">
+        <v>21.95957</v>
+      </c>
+      <c r="G48" t="n">
+        <v>34.49144</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unit 11</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>16.66467</v>
+      </c>
+      <c r="D49" t="n">
+        <v>16.13499</v>
+      </c>
+      <c r="E49" t="n">
+        <v>16.26867</v>
+      </c>
+      <c r="F49" t="n">
+        <v>21.30863</v>
+      </c>
+      <c r="G49" t="n">
+        <v>34.35807</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unit 12</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>17.02112</v>
+      </c>
+      <c r="D50" t="n">
+        <v>15.95635</v>
+      </c>
+      <c r="E50" t="n">
+        <v>16.65906</v>
+      </c>
+      <c r="F50" t="n">
+        <v>21.93963</v>
+      </c>
+      <c r="G50" t="n">
+        <v>34.42511</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Unit 13</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>16.82056</v>
+      </c>
+      <c r="D51" t="n">
+        <v>16.14899</v>
+      </c>
+      <c r="E51" t="n">
+        <v>16.52121</v>
+      </c>
+      <c r="F51" t="n">
+        <v>21.91375</v>
+      </c>
+      <c r="G51" t="n">
+        <v>34.37232</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unit 14</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>16.80853</v>
+      </c>
+      <c r="D52" t="n">
+        <v>16.35321</v>
+      </c>
+      <c r="E52" t="n">
+        <v>16.46347</v>
+      </c>
+      <c r="F52" t="n">
+        <v>21.91515</v>
+      </c>
+      <c r="G52" t="n">
+        <v>34.50266</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unit 15</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>16.47917</v>
+      </c>
+      <c r="D53" t="n">
+        <v>15.6759</v>
+      </c>
+      <c r="E53" t="n">
+        <v>16.30408</v>
+      </c>
+      <c r="F53" t="n">
+        <v>21.52915</v>
+      </c>
+      <c r="G53" t="n">
+        <v>34.28176</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unit 16</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>16.84888</v>
+      </c>
+      <c r="D54" t="n">
+        <v>16.04631</v>
+      </c>
+      <c r="E54" t="n">
+        <v>16.75717</v>
+      </c>
+      <c r="F54" t="n">
+        <v>21.1322</v>
+      </c>
+      <c r="G54" t="n">
+        <v>34.07421</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unit 17</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>16.70584</v>
+      </c>
+      <c r="D55" t="n">
+        <v>16.12207</v>
+      </c>
+      <c r="E55" t="n">
+        <v>16.39889</v>
+      </c>
+      <c r="F55" t="n">
+        <v>22.06629</v>
+      </c>
+      <c r="G55" t="n">
+        <v>34.809</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unit 18</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>16.61549</v>
+      </c>
+      <c r="D56" t="n">
+        <v>16.09326</v>
+      </c>
+      <c r="E56" t="n">
+        <v>16.59238</v>
+      </c>
+      <c r="F56" t="n">
+        <v>21.86617</v>
+      </c>
+      <c r="G56" t="n">
+        <v>33.73374</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unit 19</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>16.96242</v>
+      </c>
+      <c r="D57" t="n">
+        <v>16.15701</v>
+      </c>
+      <c r="E57" t="n">
+        <v>16.19554</v>
+      </c>
+      <c r="F57" t="n">
+        <v>21.47881</v>
+      </c>
+      <c r="G57" t="n">
+        <v>33.77434</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unit 20</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>16.78822</v>
+      </c>
+      <c r="D58" t="n">
+        <v>15.8365</v>
+      </c>
+      <c r="E58" t="n">
+        <v>16.52226</v>
+      </c>
+      <c r="F58" t="n">
+        <v>21.92394</v>
+      </c>
+      <c r="G58" t="n">
+        <v>34.2448</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unit 21</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>16.51384</v>
+      </c>
+      <c r="D59" t="n">
+        <v>15.98064</v>
+      </c>
+      <c r="E59" t="n">
+        <v>16.36725</v>
+      </c>
+      <c r="F59" t="n">
+        <v>21.64699</v>
+      </c>
+      <c r="G59" t="n">
+        <v>34.57036</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unit 22</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>16.54382</v>
+      </c>
+      <c r="D60" t="n">
+        <v>15.77506</v>
+      </c>
+      <c r="E60" t="n">
+        <v>16.28541</v>
+      </c>
+      <c r="F60" t="n">
+        <v>21.8431</v>
+      </c>
+      <c r="G60" t="n">
+        <v>34.56685</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Unit 23</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>16.82882</v>
+      </c>
+      <c r="D61" t="n">
+        <v>15.9309</v>
+      </c>
+      <c r="E61" t="n">
+        <v>16.68243</v>
+      </c>
+      <c r="F61" t="n">
+        <v>21.81682</v>
+      </c>
+      <c r="G61" t="n">
+        <v>33.5485</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Unit 24</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>16.5647</v>
+      </c>
+      <c r="D62" t="n">
+        <v>16.22244</v>
+      </c>
+      <c r="E62" t="n">
+        <v>16.29041</v>
+      </c>
+      <c r="F62" t="n">
+        <v>21.78177</v>
+      </c>
+      <c r="G62" t="n">
+        <v>34.77403</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Unit 25</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>16.80931</v>
+      </c>
+      <c r="D63" t="n">
+        <v>16.07403</v>
+      </c>
+      <c r="E63" t="n">
+        <v>16.15194</v>
+      </c>
+      <c r="F63" t="n">
+        <v>21.62797</v>
+      </c>
+      <c r="G63" t="n">
+        <v>34.07339</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Unit 26</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>16.8015</v>
+      </c>
+      <c r="D64" t="n">
+        <v>16.10263</v>
+      </c>
+      <c r="E64" t="n">
+        <v>16.1566</v>
+      </c>
+      <c r="F64" t="n">
+        <v>21.95339</v>
+      </c>
+      <c r="G64" t="n">
+        <v>34.16808</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Unit 27</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>16.74073</v>
+      </c>
+      <c r="D65" t="n">
+        <v>16.01116</v>
+      </c>
+      <c r="E65" t="n">
+        <v>16.41413</v>
+      </c>
+      <c r="F65" t="n">
+        <v>21.59933</v>
+      </c>
+      <c r="G65" t="n">
+        <v>34.31949</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Unit 28</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>16.63319</v>
+      </c>
+      <c r="D66" t="n">
+        <v>16.10529</v>
+      </c>
+      <c r="E66" t="n">
+        <v>16.19831</v>
+      </c>
+      <c r="F66" t="n">
+        <v>21.65435</v>
+      </c>
+      <c r="G66" t="n">
+        <v>33.89408</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Unit 29</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>16.50964</v>
+      </c>
+      <c r="D67" t="n">
+        <v>15.94677</v>
+      </c>
+      <c r="E67" t="n">
+        <v>16.50256</v>
+      </c>
+      <c r="F67" t="n">
+        <v>21.81429</v>
+      </c>
+      <c r="G67" t="n">
+        <v>33.75528</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Unit 30</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>16.63083</v>
+      </c>
+      <c r="D68" t="n">
+        <v>16.05613</v>
+      </c>
+      <c r="E68" t="n">
+        <v>16.4541</v>
+      </c>
+      <c r="F68" t="n">
+        <v>21.75752</v>
+      </c>
+      <c r="G68" t="n">
+        <v>34.2159</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Unit 31</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>16.50787</v>
+      </c>
+      <c r="D69" t="n">
+        <v>15.90049</v>
+      </c>
+      <c r="E69" t="n">
+        <v>16.50461</v>
+      </c>
+      <c r="F69" t="n">
+        <v>21.72453</v>
+      </c>
+      <c r="G69" t="n">
+        <v>33.83407</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Unit 32</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>16.44015</v>
+      </c>
+      <c r="D70" t="n">
+        <v>15.84066</v>
+      </c>
+      <c r="E70" t="n">
+        <v>16.34988</v>
+      </c>
+      <c r="F70" t="n">
+        <v>21.94108</v>
+      </c>
+      <c r="G70" t="n">
+        <v>34.5605</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Unit 33</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>17.05029</v>
+      </c>
+      <c r="D71" t="n">
+        <v>15.83265</v>
+      </c>
+      <c r="E71" t="n">
+        <v>16.45213</v>
+      </c>
+      <c r="F71" t="n">
+        <v>21.79011</v>
+      </c>
+      <c r="G71" t="n">
+        <v>34.3572</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Unit 34</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>16.94122</v>
+      </c>
+      <c r="D72" t="n">
+        <v>16.01761</v>
+      </c>
+      <c r="E72" t="n">
+        <v>16.25081</v>
+      </c>
+      <c r="F72" t="n">
+        <v>21.71793</v>
+      </c>
+      <c r="G72" t="n">
+        <v>33.89618</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Unit 35</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>16.67996</v>
+      </c>
+      <c r="D73" t="n">
+        <v>15.95882</v>
+      </c>
+      <c r="E73" t="n">
+        <v>16.05143</v>
+      </c>
+      <c r="F73" t="n">
+        <v>21.2372</v>
+      </c>
+      <c r="G73" t="n">
+        <v>34.01216</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Unit 36</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>16.62427</v>
+      </c>
+      <c r="D74" t="n">
+        <v>16.03973</v>
+      </c>
+      <c r="E74" t="n">
+        <v>16.57537</v>
+      </c>
+      <c r="F74" t="n">
+        <v>21.61467</v>
+      </c>
+      <c r="G74" t="n">
+        <v>34.18161</v>
       </c>
     </row>
   </sheetData>
